--- a/outputs/daily/hr_rankings_2026-08-12_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-12_full.xlsx
@@ -9362,34 +9362,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9646,34 +9642,30 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15410,34 +15402,30 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25890,34 +25878,30 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -38470,34 +38454,30 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42556,28 +42536,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr"/>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y154" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57602,34 +57586,30 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57886,34 +57866,30 @@
       </c>
       <c r="W210" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB210" t="inlineStr"/>
       <c r="AC210" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58168,28 +58144,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W211" t="inlineStr"/>
-      <c r="X211" t="inlineStr"/>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y211" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB211" t="inlineStr"/>
       <c r="AC211" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-12_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-12_full.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1015,32 +1015,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>670541</t>
+          <t>624413</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-12T19:45:00Z</t>
+          <t>2026-08-12T17:40:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Adrian Houser</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>605288</t>
+          <t>805673</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,26 +1078,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>82.8</v>
+        <v>72.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>46.6</v>
+        <v>56.3</v>
       </c>
       <c r="R3" t="n">
-        <v>48.3</v>
+        <v>44.1</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
       </c>
       <c r="T3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>10.8</v>
+        <v>100</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1149,142 +1149,142 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 13.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.6% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>16.74</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>94.56</t>
+          <t>93.92</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>105.1049</t>
+          <t>104.1891</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.6456</t>
+          <t>0.5468</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.271</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.3867</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>74.78</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>61.45</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>35.87</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2578</t>
+          <t>0.2317</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>90.06</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.4395</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1743</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr"/>
@@ -1295,32 +1295,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>624413</t>
+          <t>670541</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-12T17:40:00Z</t>
+          <t>2026-08-12T19:45:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>805673</t>
+          <t>605288</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>67</v>
+        <v>67.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1358,26 +1358,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>72.5</v>
+        <v>82.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>56.3</v>
+        <v>46.6</v>
       </c>
       <c r="R4" t="n">
-        <v>44.1</v>
+        <v>48.3</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>88.90000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1439,132 +1439,132 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.6% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.74</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>94.56</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.1891</t>
+          <t>105.1049</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5468</t>
+          <t>0.6456</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3867</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.78</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>61.45</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2317</t>
+          <t>0.2578</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>90.06</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.4395</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.1743</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7963,32 +7963,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>641933</t>
+          <t>606466</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-12T17:40:00Z</t>
+          <t>2026-08-12T19:40:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>805673</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8026,58 +8026,54 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>48.6</v>
+        <v>49.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>56.3</v>
+        <v>46.5</v>
       </c>
       <c r="R28" t="n">
-        <v>44.1</v>
+        <v>41.7</v>
       </c>
       <c r="S28" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U28" t="n">
-        <v>54.4</v>
+        <v>54.7</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8097,12 +8093,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -8117,122 +8113,122 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.6% barrel, 15.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.1% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>100.4288</t>
+          <t>102.2165</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.4376</t>
+          <t>0.4878</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.2191</t>
+          <t>0.2091</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.3236</t>
+          <t>0.3606</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.2095</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>88.32</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.4512</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.2003</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -8243,47 +8239,47 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>606466</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-12T19:40:00Z</t>
+          <t>2026-08-12T23:40:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8306,39 +8302,47 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>49.7</v>
+        <v>55.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.5</v>
+        <v>51.9</v>
       </c>
       <c r="R29" t="n">
-        <v>41.7</v>
+        <v>27.6</v>
       </c>
       <c r="S29" t="n">
-        <v>94.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T29" t="n">
         <v>75</v>
       </c>
       <c r="U29" t="n">
-        <v>54.7</v>
+        <v>48.7</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z29" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8346,12 +8350,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -8373,7 +8377,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -8393,122 +8397,114 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.1% barrel, 13.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.9% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>102.2165</t>
+          <t>104.001</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.4878</t>
+          <t>0.4646</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.2091</t>
+          <t>0.1982</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3606</t>
+          <t>0.3521</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>75.17</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>52.72</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>35.03</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.2095</t>
+          <t>0.2103</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4512</t>
+          <t>0.4418</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.2003</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>28.95</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>28.07</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8519,47 +8515,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>682829</t>
+          <t>676475</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-12T23:40:00Z</t>
+          <t>2026-08-12T18:15:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>554430</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8568,7 +8564,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8582,62 +8578,58 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>55.9</v>
+        <v>53.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>51.9</v>
+        <v>23.9</v>
       </c>
       <c r="R30" t="n">
-        <v>27.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U30" t="n">
-        <v>48.7</v>
+        <v>34.4</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8662,129 +8654,137 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.9% barrel, 18.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.4% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>91.56</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>104.001</t>
+          <t>101.9076</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4646</t>
+          <t>0.5172</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1982</t>
+          <t>0.2284</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3521</t>
+          <t>0.3716</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>75.17</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>52.72</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>35.03</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.2103</t>
+          <t>0.1865</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.4418</t>
+          <t>0.3151</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.1156</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>28.07</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr"/>
-      <c r="BH30" t="inlineStr"/>
+          <t>25.95</t>
+        </is>
+      </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8795,27 +8795,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>676475</t>
+          <t>691016</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Tyler Soderstrom</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-12T18:15:00Z</t>
+          <t>2026-08-12T19:05:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8825,17 +8825,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>554430</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8858,26 +8858,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>53.5</v>
+        <v>45.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>23.9</v>
+        <v>29.4</v>
       </c>
       <c r="R31" t="n">
-        <v>70.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="S31" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T31" t="n">
         <v>80</v>
       </c>
       <c r="U31" t="n">
-        <v>34.4</v>
+        <v>60.7</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -8929,27 +8929,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.4% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -8959,97 +8959,97 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>91.56</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>101.9076</t>
+          <t>102.1382</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.5172</t>
+          <t>0.4269</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.2284</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3716</t>
+          <t>0.334</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1865</t>
+          <t>0.2197</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>88.71</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.3151</t>
+          <t>0.3561</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.1156</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -9075,56 +9075,56 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>691016</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tyler Soderstrom</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-12T19:05:00Z</t>
+          <t>2026-08-13T02:10:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Daniel Lynch IV</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>663738</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>56.4</v>
+        <v>56.3</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9138,58 +9138,62 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>45.3</v>
+        <v>80</v>
       </c>
       <c r="Q32" t="n">
-        <v>29.4</v>
+        <v>25.7</v>
       </c>
       <c r="R32" t="n">
-        <v>67.40000000000001</v>
+        <v>27.6</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>88.7</v>
       </c>
       <c r="T32" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U32" t="n">
-        <v>60.7</v>
+        <v>54.9</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9214,7 +9218,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9229,122 +9233,114 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 13.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>93.78</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>102.1382</t>
+          <t>104.3548</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.4269</t>
+          <t>0.5909</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>74.96</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>52.45</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>47.19</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>32.41</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.2197</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.71</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.3561</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1305</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>22.96</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
+          <t>24.51</t>
+        </is>
+      </c>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9355,27 +9351,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>687605</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Andrew Pinckney</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-13T02:10:00Z</t>
+          <t>2026-08-12T22:45:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9385,17 +9381,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Daniel Lynch IV</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>663738</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9404,7 +9400,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>56.3</v>
+        <v>56.1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9418,26 +9414,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>80</v>
+        <v>72.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>25.7</v>
+        <v>37.4</v>
       </c>
       <c r="R33" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="S33" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T33" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U33" t="n">
-        <v>54.9</v>
+        <v>37.8</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9451,7 +9447,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -9476,7 +9472,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9488,139 +9484,139 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 4 games: 1/4, 1 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>104.3548</t>
+          <t>98.9195</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.5909</t>
+          <t>0.618</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.381</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>52.45</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>47.19</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.1305</t>
+          <t>0.1454</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9631,27 +9627,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>687605</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Andrew Pinckney</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-12T22:45:00Z</t>
+          <t>2026-08-13T02:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9661,26 +9657,26 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>George Klassen</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>691946</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>56.1</v>
+        <v>55.9</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9694,26 +9690,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>72.5</v>
+        <v>50.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>37.4</v>
+        <v>45.7</v>
       </c>
       <c r="R34" t="n">
         <v>28.2</v>
       </c>
       <c r="S34" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T34" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>37.8</v>
+        <v>81.7</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9727,7 +9723,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9752,7 +9748,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9764,139 +9760,139 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 4 games: 1/4, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>51.46</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>98.9195</t>
+          <t>102.2082</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>0.4778</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>0.1964</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.3574</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>27.11</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1454</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr"/>
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9907,27 +9903,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>677800</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-13T02:10:00Z</t>
+          <t>2026-08-12T23:07:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9937,17 +9933,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>George Klassen</t>
+          <t>José Soriano</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>691946</t>
+          <t>667755</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9956,7 +9952,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -9974,22 +9970,22 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>50.8</v>
+        <v>54.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>45.7</v>
+        <v>36.4</v>
       </c>
       <c r="R35" t="n">
-        <v>28.2</v>
+        <v>30.4</v>
       </c>
       <c r="S35" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T35" t="n">
         <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>81.7</v>
+        <v>91.5</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10003,7 +9999,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10028,7 +10024,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -10045,134 +10041,134 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.24</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>102.2082</t>
+          <t>101.3032</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4778</t>
+          <t>0.4792</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1964</t>
+          <t>0.2271</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3574</t>
+          <t>0.3462</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>27.11</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>37.41</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.2129</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.3782</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1362</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10183,47 +10179,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>677800</t>
+          <t>641933</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-12T23:07:00Z</t>
+          <t>2026-08-12T17:40:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>667755</t>
+          <t>805673</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10232,7 +10228,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>55.8</v>
+        <v>55.5</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10246,62 +10242,58 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>54.1</v>
+        <v>48.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>36.4</v>
+        <v>56.3</v>
       </c>
       <c r="R36" t="n">
-        <v>30.4</v>
+        <v>44.1</v>
       </c>
       <c r="S36" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U36" t="n">
-        <v>91.5</v>
+        <v>31.9</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10321,27 +10313,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.6% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10351,104 +10343,112 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>41.41</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>90.24</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>101.3032</t>
+          <t>100.4288</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4792</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.2271</t>
+          <t>0.2191</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3462</t>
+          <t>0.3236</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.2129</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.3782</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1362</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>18.82</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr"/>
-      <c r="BH36" t="inlineStr"/>
+          <t>27.66</t>
+        </is>
+      </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -12411,32 +12411,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>665019</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-12T18:15:00Z</t>
+          <t>2026-08-12T17:40:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -12446,12 +12446,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Shane Baz</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>554430</t>
+          <t>669358</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12474,26 +12474,26 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>55.3</v>
+        <v>51.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.9</v>
+        <v>40.3</v>
       </c>
       <c r="R44" t="n">
-        <v>70.59999999999999</v>
+        <v>44.1</v>
       </c>
       <c r="S44" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T44" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U44" t="n">
-        <v>46.9</v>
+        <v>19.9</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12545,12 +12545,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -12560,127 +12560,127 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 1 HR</t>
+          <t>Last 7 games: 3/23, 1 HR</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.41</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>92.51</t>
+          <t>92.13</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>104.7276</t>
+          <t>101.4204</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.4484</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.2006</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.3312</t>
+          <t>0.3247</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>71.99</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.1701</t>
+          <t>0.2287</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.3151</t>
+          <t>0.3951</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.1156</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12691,32 +12691,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-12T17:40:00Z</t>
+          <t>2026-08-12T18:15:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -12726,12 +12726,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Shane Baz</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>669358</t>
+          <t>554430</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12740,7 +12740,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12754,26 +12754,26 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>51.2</v>
+        <v>55.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>40.3</v>
+        <v>23.9</v>
       </c>
       <c r="R45" t="n">
-        <v>44.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S45" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T45" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>18.3</v>
+        <v>46.9</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12825,12 +12825,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -12840,127 +12840,127 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 1 HR</t>
+          <t>Last 7 games: 9/29, 1 HR</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 14.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>48.11</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>92.13</t>
+          <t>92.51</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>101.4204</t>
+          <t>104.7276</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.4484</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.2006</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.3247</t>
+          <t>0.3312</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>71.99</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.2287</t>
+          <t>0.1701</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.3951</t>
+          <t>0.3151</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.1156</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>93</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>80</v>
       </c>
       <c r="U72" t="n">
-        <v>36.3</v>
+        <v>37.8</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
@@ -25172,7 +25172,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -26231,47 +26231,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>672515</t>
+          <t>687637</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-12T19:40:00Z</t>
+          <t>2026-08-12T17:40:00Z</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>805673</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -26294,54 +26294,58 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>34.9</v>
+        <v>28.8</v>
       </c>
       <c r="Q94" t="n">
-        <v>48</v>
+        <v>56.3</v>
       </c>
       <c r="R94" t="n">
-        <v>41.7</v>
+        <v>44.1</v>
       </c>
       <c r="S94" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T94" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U94" t="n">
-        <v>37.6</v>
+        <v>5.7</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y94" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26361,12 +26365,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -26376,12 +26380,12 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Contact streak: 10/27 over last 7 games</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 13.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.6% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
@@ -26391,112 +26395,112 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>42.49</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>99.5272</t>
+          <t>99.2112</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>0.4537</t>
+          <t>0.3786</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>0.1628</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>0.3635</t>
+          <t>0.3181</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>35.78</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>0.1473</t>
+          <t>0.117</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>0.4512</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
-          <t>0.2003</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="BG94" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI94" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ94" t="inlineStr"/>
@@ -26507,47 +26511,47 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>687637</t>
+          <t>672515</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-12T17:40:00Z</t>
+          <t>2026-08-12T19:40:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>805673</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -26556,7 +26560,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26570,58 +26574,54 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>28.8</v>
+        <v>34.9</v>
       </c>
       <c r="Q95" t="n">
-        <v>56.3</v>
+        <v>48</v>
       </c>
       <c r="R95" t="n">
-        <v>44.1</v>
+        <v>41.7</v>
       </c>
       <c r="S95" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T95" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U95" t="n">
-        <v>3.4</v>
+        <v>37.6</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC95" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26641,12 +26641,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26656,12 +26656,12 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Contact streak: 10/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.6% barrel, 15.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26671,112 +26671,112 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>42.49</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>99.2112</t>
+          <t>99.5272</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.3786</t>
+          <t>0.4537</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.1628</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3181</t>
+          <t>0.3635</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>35.78</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>25.47</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.1473</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>88.32</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.4512</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.2003</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -26812,7 +26812,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -29588,7 +29588,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -31256,7 +31256,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -35392,7 +35392,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -38980,7 +38980,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -46200,7 +46200,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -50056,7 +50056,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -58584,7 +58584,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -62967,12 +62967,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>668952</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -62997,7 +62997,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -63016,7 +63016,7 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>11</v>
+        <v>26.1</v>
       </c>
       <c r="Q227" t="n">
         <v>40.3</v>
@@ -63043,13 +63043,13 @@
         <v>44.1</v>
       </c>
       <c r="S227" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T227" t="n">
         <v>50</v>
       </c>
       <c r="U227" t="n">
-        <v>25.8</v>
+        <v>17.3</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -63101,12 +63101,12 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
@@ -63116,7 +63116,7 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
@@ -63131,67 +63131,67 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>96.603</t>
+          <t>99.1869</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3549</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.1343</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.3142</t>
+          <t>0.2759</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>73.17</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>26.83</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
@@ -63247,12 +63247,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>668952</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -63277,7 +63277,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -63296,7 +63296,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
@@ -63314,7 +63314,7 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>26.1</v>
+        <v>11</v>
       </c>
       <c r="Q228" t="n">
         <v>40.3</v>
@@ -63323,13 +63323,13 @@
         <v>44.1</v>
       </c>
       <c r="S228" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T228" t="n">
         <v>50</v>
       </c>
       <c r="U228" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -63343,7 +63343,7 @@
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
@@ -63381,7 +63381,7 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
@@ -63396,7 +63396,7 @@
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
@@ -63411,67 +63411,67 @@
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>85.08</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>99.1869</t>
+          <t>96.603</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3549</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.1343</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.2759</t>
+          <t>0.3142</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>73.17</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>26.83</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
@@ -64384,7 +64384,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -69364,7 +69364,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -75786,7 +75786,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -76041,32 +76041,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>670541</t>
+          <t>624413</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-12T19:45:00Z</t>
+          <t>2026-08-12T17:40:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -76076,12 +76076,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Adrian Houser</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>605288</t>
+          <t>805673</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -76090,7 +76090,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -76104,26 +76104,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>82.8</v>
+        <v>72.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>46.6</v>
+        <v>56.3</v>
       </c>
       <c r="R3" t="n">
-        <v>48.3</v>
+        <v>44.1</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
       </c>
       <c r="T3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>10.8</v>
+        <v>100</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -76175,142 +76175,142 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 13.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.6% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>16.74</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>94.56</t>
+          <t>93.92</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>105.1049</t>
+          <t>104.1891</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.6456</t>
+          <t>0.5468</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.271</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.3867</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>74.78</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>61.45</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>35.87</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2578</t>
+          <t>0.2317</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>90.06</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.4395</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1743</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr"/>
@@ -76321,32 +76321,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>624413</t>
+          <t>670541</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-12T17:40:00Z</t>
+          <t>2026-08-12T19:45:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -76356,12 +76356,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>805673</t>
+          <t>605288</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -76370,7 +76370,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>67</v>
+        <v>67.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -76384,26 +76384,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>72.5</v>
+        <v>82.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>56.3</v>
+        <v>46.6</v>
       </c>
       <c r="R4" t="n">
-        <v>44.1</v>
+        <v>48.3</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>88.90000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -76455,7 +76455,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -76465,132 +76465,132 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.6% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.74</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>94.56</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.1891</t>
+          <t>105.1049</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5468</t>
+          <t>0.6456</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3867</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.78</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>61.45</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2317</t>
+          <t>0.2578</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>90.06</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.4395</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.1743</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -76902,7 +76902,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
